--- a/Relatorios_Auditoria/template_4_Teste_Regra_R4.xlsx
+++ b/Relatorios_Auditoria/template_4_Teste_Regra_R4.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,58 +518,66 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fazenda Pública</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
+          <t>Valor Pagamento Parcial (R$)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Honorários Sucumbência (%)</t>
+          <t>Fazenda Pública</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Base Honorários</t>
+          <t>Honorários Sucumbência (%)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONDENAÇÃO</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Proporção Honorários (%)</t>
+          <t>Base Honorários</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>CONDENAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Proporção Honorários (%)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Proporção Custas (%)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>100</t>
         </is>
